--- a/selection_55_maladies_avec_resume.xlsx
+++ b/selection_55_maladies_avec_resume.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melan\DESU_DATA_2026\projet_DESU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD284BA6-571C-4371-BC62-61FE94214EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9A659A-3921-4C5E-8851-73CC4E279BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="172">
   <si>
     <t>Category</t>
   </si>
@@ -359,9 +359,6 @@
     <t>Afrique subsaharienne, Asie du Sud</t>
   </si>
   <si>
-    <t>80–85</t>
-  </si>
-  <si>
     <t>Europe et Amérique du Nord</t>
   </si>
   <si>
@@ -374,9 +371,6 @@
     <t>pays à haut revenu et revenus intermédiaires</t>
   </si>
   <si>
-    <t>65–75</t>
-  </si>
-  <si>
     <t>pics en Europe centrale et orientale</t>
   </si>
   <si>
@@ -386,87 +380,48 @@
     <t>3 %</t>
   </si>
   <si>
-    <t>50–65</t>
-  </si>
-  <si>
-    <t>44–45</t>
-  </si>
-  <si>
     <t>Interstitial lung disease</t>
   </si>
   <si>
     <t>Pulmonary sarcoidosis</t>
   </si>
   <si>
-    <t>60-75</t>
-  </si>
-  <si>
     <t>France, pays occidentaux</t>
   </si>
   <si>
-    <t>25–45</t>
-  </si>
-  <si>
     <t>Pays nordiques, populations afro‑descendantes</t>
   </si>
   <si>
-    <t>&gt; 60</t>
-  </si>
-  <si>
     <t>Pays occidentaux</t>
   </si>
   <si>
     <t>pays occidentaux à haut revenu</t>
   </si>
   <si>
-    <t>30–40</t>
-  </si>
-  <si>
-    <t>20–40</t>
-  </si>
-  <si>
     <t>France et pays industrialisés</t>
   </si>
   <si>
     <t>pays occidentaux</t>
   </si>
   <si>
-    <t>&lt;20</t>
-  </si>
-  <si>
     <t>Pays à haut revenu et à revenu intermédiaire</t>
   </si>
   <si>
     <t>3/1000</t>
   </si>
   <si>
-    <t>40–50</t>
-  </si>
-  <si>
     <t>Pays occidentaux à haut revenu</t>
   </si>
   <si>
-    <t>&gt;60</t>
-  </si>
-  <si>
-    <t>60–65</t>
-  </si>
-  <si>
     <t>Canada, Russie, Afrique du Nord &amp; Moyen‑Orient</t>
   </si>
   <si>
     <t>Asie, Europe de l’Est, certaines régions de l’Amérique latine</t>
   </si>
   <si>
-    <t>50–60</t>
-  </si>
-  <si>
     <t>Amériques et Europe de l’Est, Afrique et Asie</t>
   </si>
   <si>
-    <t>30-60</t>
-  </si>
-  <si>
     <t>Amériques et populations afro‑descendantes, certaines populations asiatiques</t>
   </si>
   <si>
@@ -482,168 +437,48 @@
     <t>Afrique subsaharienne, Afrique centrale et de l’Ouest, Inde, Moyen‑Orient, Caraïbes</t>
   </si>
   <si>
-    <t>&gt;40</t>
-  </si>
-  <si>
     <t>Afrique du Nord &amp; Moyen‑Orient, Amérique latine/Caraïbes, pays à revenu faible ou intermédiaire</t>
   </si>
   <si>
-    <t>30–50</t>
-  </si>
-  <si>
     <t>Afrique subsaharienne, Moyen‑Orient, Inde, Asie du Sud‑Est</t>
   </si>
   <si>
-    <t>15-35</t>
-  </si>
-  <si>
     <t>Pathologie mondiale</t>
   </si>
   <si>
-    <t>19-20</t>
-  </si>
-  <si>
     <t>1/1000</t>
   </si>
   <si>
-    <t>20-30</t>
-  </si>
-  <si>
-    <t>40-50</t>
-  </si>
-  <si>
-    <t>25-44</t>
-  </si>
-  <si>
     <t>Pays à haut revenu et certaines populations à risque</t>
   </si>
   <si>
-    <t>40-60</t>
-  </si>
-  <si>
-    <t>&lt;16</t>
-  </si>
-  <si>
-    <t>&gt;55</t>
-  </si>
-  <si>
     <t>Monde entier, plus forte charge dans les pays à revenu faible ou intermédiaire</t>
   </si>
   <si>
-    <t>45-55</t>
-  </si>
-  <si>
     <t>Asie</t>
   </si>
   <si>
-    <t>60-70</t>
-  </si>
-  <si>
-    <t>65–71</t>
-  </si>
-  <si>
-    <t>60–70</t>
-  </si>
-  <si>
     <t>pays à revenu faible ou intermédiaire</t>
   </si>
   <si>
-    <t>50–53</t>
-  </si>
-  <si>
     <t>Asie de l’Est</t>
   </si>
   <si>
-    <t>60–75</t>
-  </si>
-  <si>
-    <t>65–80</t>
-  </si>
-  <si>
     <t>Amérique du Nord / Europe occidentale / Australie</t>
   </si>
   <si>
-    <t>50–70</t>
-  </si>
-  <si>
     <t>Océanie / Europe / Amérique du Nord</t>
   </si>
   <si>
-    <t>40–70</t>
-  </si>
-  <si>
-    <t>70–85</t>
-  </si>
-  <si>
-    <t>0–20</t>
-  </si>
-  <si>
-    <t>75–90</t>
-  </si>
-  <si>
-    <t>0-18</t>
-  </si>
-  <si>
-    <t>20–60</t>
-  </si>
-  <si>
-    <t>25-55</t>
-  </si>
-  <si>
     <t>Pays industrialisés / populations âgées</t>
   </si>
   <si>
-    <t>60-80</t>
-  </si>
-  <si>
-    <t>65–90</t>
-  </si>
-  <si>
-    <t>70-90</t>
-  </si>
-  <si>
     <t>Pays tropicaux à faibles ressources</t>
   </si>
   <si>
-    <t>0-20</t>
-  </si>
-  <si>
-    <t>20-60</t>
-  </si>
-  <si>
-    <t>0-40</t>
-  </si>
-  <si>
-    <t>tout age</t>
-  </si>
-  <si>
-    <t>60–85</t>
-  </si>
-  <si>
-    <t>30–70</t>
-  </si>
-  <si>
-    <t>20-45</t>
-  </si>
-  <si>
-    <t>20–50</t>
-  </si>
-  <si>
-    <t>25-40</t>
-  </si>
-  <si>
     <t>pubmed</t>
   </si>
   <si>
-    <t>15-40</t>
-  </si>
-  <si>
-    <t>15-45</t>
-  </si>
-  <si>
-    <t>50–80</t>
-  </si>
-  <si>
     <t>Femmes</t>
   </si>
   <si>
@@ -698,12 +533,6 @@
     <t>Interstitial nephritis</t>
   </si>
   <si>
-    <t>50-80</t>
-  </si>
-  <si>
-    <t>55-75</t>
-  </si>
-  <si>
     <t>Pays industrialisés</t>
   </si>
   <si>
@@ -713,25 +542,13 @@
     <t>Amérique du Nord / Europe / Asie</t>
   </si>
   <si>
-    <t>50-75</t>
-  </si>
-  <si>
     <t>Europe / Amérique du Nord</t>
   </si>
   <si>
-    <t>55-80</t>
-  </si>
-  <si>
     <t>Europe, Amérique du Nord, Afrique du Nord, Asie de l’Ouest</t>
   </si>
   <si>
-    <t>20-50</t>
-  </si>
-  <si>
-    <t>30-50</t>
-  </si>
-  <si>
-    <t>40-70</t>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -1159,10 +976,10 @@
         <v>106</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>203</v>
+        <v>148</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -1185,7 +1002,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="G2" s="6">
         <v>0.5</v>
@@ -1237,7 +1054,7 @@
         <v>220</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E4" s="6">
         <v>5.0000000000000001E-4</v>
@@ -1246,13 +1063,13 @@
         <v>1.2E-4</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="H4" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="4">
+        <v>82</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -1281,7 +1098,7 @@
         <v>103</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1339,7 +1156,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -1368,7 +1185,7 @@
         <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1393,11 +1210,11 @@
       <c r="G9" s="6">
         <v>0.4</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>113</v>
+      <c r="H9" s="4">
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1422,11 +1239,11 @@
       <c r="G10" s="6">
         <v>0.45</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="4">
+        <v>70</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1451,11 +1268,11 @@
       <c r="G11" s="6">
         <v>0.5</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>117</v>
+      <c r="H11" s="4">
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1463,7 +1280,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3">
         <v>41582</v>
@@ -1484,7 +1301,7 @@
         <v>60</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1509,11 +1326,11 @@
       <c r="G13" s="6">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>118</v>
+      <c r="H13" s="4">
+        <v>45</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1521,7 +1338,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C14" s="3">
         <v>111248</v>
@@ -1538,11 +1355,11 @@
       <c r="G14" s="6">
         <v>0.7</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>121</v>
+      <c r="H14" s="4">
+        <v>67</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1550,7 +1367,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3">
         <v>11885</v>
@@ -1567,11 +1384,11 @@
       <c r="G15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>123</v>
+      <c r="H15" s="4">
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1596,11 +1413,11 @@
       <c r="G16" s="6">
         <v>0.5</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>125</v>
+      <c r="H16" s="4">
+        <v>60</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1629,7 +1446,7 @@
         <v>50</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1654,11 +1471,11 @@
       <c r="G18" s="6">
         <v>0.5</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>129</v>
+      <c r="H18" s="4">
+        <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1683,11 +1500,11 @@
       <c r="G19" s="6">
         <v>0.25</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>128</v>
+      <c r="H19" s="4">
+        <v>35</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1712,11 +1529,11 @@
       <c r="G20" s="6">
         <v>0.7</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>123</v>
+      <c r="H20" s="4">
+        <v>35</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1741,11 +1558,11 @@
       <c r="G21" s="6">
         <v>0.5</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>132</v>
+      <c r="H21" s="4">
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1762,7 +1579,7 @@
         <v>0.15</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F22" s="6">
         <v>0</v>
@@ -1770,11 +1587,11 @@
       <c r="G22" s="6">
         <v>0.7</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>135</v>
+      <c r="H22" s="4">
+        <v>45</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1799,11 +1616,11 @@
       <c r="G23" s="6">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>137</v>
+      <c r="H23" s="4">
+        <v>60</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1828,11 +1645,11 @@
       <c r="G24" s="6">
         <v>0.52</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>138</v>
+      <c r="H24" s="4">
+        <v>62</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1857,11 +1674,11 @@
       <c r="G25" s="6">
         <v>0.5</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>141</v>
+      <c r="H25" s="4">
+        <v>55</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1886,11 +1703,11 @@
       <c r="G26" s="6">
         <v>0.8</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>143</v>
+      <c r="H26" s="4">
+        <v>45</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1915,11 +1732,11 @@
       <c r="G27" s="6">
         <v>0.9</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="4">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1948,7 +1765,7 @@
         <v>50</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1977,7 +1794,7 @@
         <v>103</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -2002,11 +1819,11 @@
       <c r="G30" s="6">
         <v>0.5</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="4">
+        <v>10</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -2031,11 +1848,11 @@
       <c r="G31" s="6">
         <v>0.5</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>132</v>
+      <c r="H31" s="4">
+        <v>10</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -2060,11 +1877,11 @@
       <c r="G32" s="6">
         <v>0.5</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>149</v>
+      <c r="H32" s="4">
+        <v>40</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -2089,11 +1906,11 @@
       <c r="G33" s="6">
         <v>0.7</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>151</v>
+      <c r="H33" s="4">
+        <v>40</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -2122,7 +1939,7 @@
         <v>103</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -2151,7 +1968,7 @@
         <v>10</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -2176,11 +1993,11 @@
       <c r="G36" s="6">
         <v>0.45</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>153</v>
+      <c r="H36" s="4">
+        <v>25</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -2209,7 +2026,7 @@
         <v>20</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -2234,11 +2051,11 @@
       <c r="G38" s="6">
         <v>0.6</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>155</v>
+      <c r="H38" s="4">
+        <v>20</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -2255,7 +2072,7 @@
         <v>0.01</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="F39" s="6">
         <v>0.2</v>
@@ -2263,11 +2080,11 @@
       <c r="G39" s="6">
         <v>0.5</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>157</v>
+      <c r="H39" s="4">
+        <v>25</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -2292,11 +2109,11 @@
       <c r="G40" s="6">
         <v>0.65</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>158</v>
+      <c r="H40" s="4">
+        <v>45</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -2325,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -2350,11 +2167,11 @@
       <c r="G42" s="6">
         <v>0.7</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>159</v>
+      <c r="H42" s="4">
+        <v>35</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -2383,7 +2200,7 @@
         <v>103</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2412,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2437,11 +2254,11 @@
       <c r="G45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>143</v>
+      <c r="H45" s="4">
+        <v>45</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2466,11 +2283,11 @@
       <c r="G46" s="6">
         <v>0.9</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>143</v>
+      <c r="H46" s="4">
+        <v>45</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2495,11 +2312,11 @@
       <c r="G47" s="6">
         <v>0.25</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>158</v>
+      <c r="H47" s="4">
+        <v>45</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2524,11 +2341,11 @@
       <c r="G48" s="6">
         <v>0.5</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>143</v>
+      <c r="H48" s="4">
+        <v>45</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2553,11 +2370,11 @@
       <c r="G49" s="6">
         <v>0.75</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>161</v>
+      <c r="H49" s="4">
+        <v>50</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2582,11 +2399,11 @@
       <c r="G50" s="6">
         <v>0.65</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>162</v>
+      <c r="H50" s="4">
+        <v>15</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2611,11 +2428,11 @@
       <c r="G51" s="6">
         <v>0.6</v>
       </c>
-      <c r="H51" s="4" t="s">
-        <v>163</v>
+      <c r="H51" s="4">
+        <v>60</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2640,11 +2457,11 @@
       <c r="G52" s="6">
         <v>0.75</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>165</v>
+      <c r="H52" s="4">
+        <v>50</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2669,11 +2486,11 @@
       <c r="G53" s="6">
         <v>0.2</v>
       </c>
-      <c r="H53" s="4" t="s">
-        <v>167</v>
+      <c r="H53" s="4">
+        <v>65</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2698,11 +2515,11 @@
       <c r="G54" s="6">
         <v>0.35</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>168</v>
+      <c r="H54" s="3">
+        <v>67</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2727,11 +2544,11 @@
       <c r="G55" s="6">
         <v>0.4</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>169</v>
+      <c r="H55" s="3">
+        <v>65</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2756,11 +2573,11 @@
       <c r="G56" s="6">
         <v>1</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>171</v>
+      <c r="H56" s="3">
+        <v>51</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2785,11 +2602,11 @@
       <c r="G57" s="6">
         <v>0.35</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>173</v>
+      <c r="H57" s="3">
+        <v>67</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2814,11 +2631,11 @@
       <c r="G58" s="6">
         <v>0.1</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>174</v>
+      <c r="H58" s="3">
+        <v>72</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2843,11 +2660,11 @@
       <c r="G59" s="6">
         <v>0.4</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>173</v>
+      <c r="H59" s="3">
+        <v>67</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2872,11 +2689,11 @@
       <c r="G60" s="6">
         <v>0.5</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>176</v>
+      <c r="H60" s="3">
+        <v>60</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2901,11 +2718,11 @@
       <c r="G61" s="6">
         <v>0.99</v>
       </c>
-      <c r="H61" s="3" t="s">
-        <v>176</v>
+      <c r="H61" s="3">
+        <v>60</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2913,7 +2730,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="C62" s="3">
         <v>36970</v>
@@ -2930,11 +2747,11 @@
       <c r="G62" s="6">
         <v>0.5</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>221</v>
+      <c r="H62" s="3">
+        <v>65</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2942,7 +2759,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="C63" s="3">
         <v>158219</v>
@@ -2959,11 +2776,11 @@
       <c r="G63" s="6">
         <v>1</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>222</v>
+      <c r="H63" s="3">
+        <v>65</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2971,7 +2788,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C64" s="3">
         <v>178997</v>
@@ -2988,11 +2805,11 @@
       <c r="G64" s="6">
         <v>1</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>167</v>
+      <c r="H64" s="3">
+        <v>65</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -3000,7 +2817,7 @@
         <v>58</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C65" s="3">
         <v>377283</v>
@@ -3017,11 +2834,11 @@
       <c r="G65" s="6">
         <v>0.25</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>121</v>
+      <c r="H65" s="3">
+        <v>67</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -3029,7 +2846,7 @@
         <v>58</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="C66" s="3">
         <v>165838</v>
@@ -3046,11 +2863,11 @@
       <c r="G66" s="6">
         <v>0.5</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>186</v>
+      <c r="H66" s="3">
+        <v>70</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -3058,7 +2875,7 @@
         <v>58</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="C67" s="3">
         <v>402993</v>
@@ -3079,7 +2896,7 @@
         <v>103</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -3087,7 +2904,7 @@
         <v>58</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="C68" s="3">
         <v>292653</v>
@@ -3104,11 +2921,11 @@
       <c r="G68" s="6">
         <v>0.5</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>226</v>
+      <c r="H68" s="3">
+        <v>62</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -3116,7 +2933,7 @@
         <v>58</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="C69" s="3">
         <v>110680</v>
@@ -3133,11 +2950,11 @@
       <c r="G69" s="6">
         <v>0.25</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>228</v>
+      <c r="H69" s="3">
+        <v>67</v>
       </c>
       <c r="I69" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -3162,11 +2979,11 @@
       <c r="G70" s="6">
         <v>0.45</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>178</v>
+      <c r="H70" s="3">
+        <v>55</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -3191,11 +3008,11 @@
       <c r="G71" s="6">
         <v>0.45</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>173</v>
+      <c r="H71" s="3">
+        <v>67</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -3220,11 +3037,11 @@
       <c r="G72" s="6">
         <v>0.4</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>179</v>
+      <c r="H72" s="3">
+        <v>77</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -3249,11 +3066,11 @@
       <c r="G73" s="6">
         <v>0.5</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>180</v>
+      <c r="H73" s="3">
+        <v>10</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -3278,11 +3095,11 @@
       <c r="G74" s="6">
         <v>0.5</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>180</v>
+      <c r="H74" s="3">
+        <v>10</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -3307,11 +3124,11 @@
       <c r="G75" s="6">
         <v>0.65</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>181</v>
+      <c r="H75" s="3">
+        <v>82</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -3336,11 +3153,11 @@
       <c r="G76" s="6">
         <v>0.45</v>
       </c>
-      <c r="H76" s="4" t="s">
-        <v>182</v>
+      <c r="H76" s="4">
+        <v>9</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -3365,11 +3182,11 @@
       <c r="G77" s="6">
         <v>0.6</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>183</v>
+      <c r="H77" s="3">
+        <v>40</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -3394,11 +3211,11 @@
       <c r="G78" s="6">
         <v>0.75</v>
       </c>
-      <c r="H78" s="4" t="s">
-        <v>184</v>
+      <c r="H78" s="4">
+        <v>40</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -3406,7 +3223,7 @@
         <v>69</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="C79" s="3">
         <v>127831</v>
@@ -3423,11 +3240,11 @@
       <c r="G79" s="6">
         <v>0.75</v>
       </c>
-      <c r="H79" s="4" t="s">
-        <v>230</v>
+      <c r="H79" s="4">
+        <v>35</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
@@ -3435,7 +3252,7 @@
         <v>69</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="C80" s="3">
         <v>4939</v>
@@ -3452,11 +3269,11 @@
       <c r="G80" s="6">
         <v>0.7</v>
       </c>
-      <c r="H80" s="4" t="s">
-        <v>230</v>
+      <c r="H80" s="4">
+        <v>35</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
@@ -3481,11 +3298,11 @@
       <c r="G81" s="6">
         <v>0.65</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>181</v>
+      <c r="H81" s="3">
+        <v>82</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
@@ -3514,7 +3331,7 @@
         <v>103</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -3539,11 +3356,11 @@
       <c r="G83" s="6">
         <v>0.5</v>
       </c>
-      <c r="H83" s="4" t="s">
-        <v>186</v>
+      <c r="H83" s="4">
+        <v>70</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
@@ -3568,11 +3385,11 @@
       <c r="G84" s="6">
         <v>0.5</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>187</v>
+      <c r="H84" s="3">
+        <v>77</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
@@ -3597,11 +3414,11 @@
       <c r="G85" s="6">
         <v>0.6</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>187</v>
+      <c r="H85" s="3">
+        <v>77</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -3626,11 +3443,11 @@
       <c r="G86" s="6">
         <v>0.6</v>
       </c>
-      <c r="H86" s="4" t="s">
-        <v>188</v>
+      <c r="H86" s="4">
+        <v>80</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
@@ -3655,11 +3472,11 @@
       <c r="G87" s="6">
         <v>0.5</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>183</v>
+      <c r="H87" s="3">
+        <v>40</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -3688,7 +3505,7 @@
         <v>103</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
@@ -3713,11 +3530,11 @@
       <c r="G89" s="6">
         <v>0.6</v>
       </c>
-      <c r="H89" s="4" t="s">
-        <v>190</v>
+      <c r="H89" s="4">
+        <v>10</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
@@ -3746,7 +3563,7 @@
         <v>20</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
@@ -3771,11 +3588,11 @@
       <c r="G91" s="6">
         <v>0.6</v>
       </c>
-      <c r="H91" s="4" t="s">
-        <v>191</v>
+      <c r="H91" s="4">
+        <v>40</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -3800,11 +3617,11 @@
       <c r="G92" s="6">
         <v>0.5</v>
       </c>
-      <c r="H92" s="4" t="s">
-        <v>192</v>
+      <c r="H92" s="4">
+        <v>20</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
@@ -3830,10 +3647,10 @@
         <v>0.5</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
@@ -3858,11 +3675,11 @@
       <c r="G94" s="6">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>194</v>
+      <c r="H94" s="3">
+        <v>72</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
@@ -3887,11 +3704,11 @@
       <c r="G95" s="6">
         <v>0.45</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>195</v>
+      <c r="H95" s="3">
+        <v>50</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
@@ -3916,11 +3733,11 @@
       <c r="G96" s="6">
         <v>1</v>
       </c>
-      <c r="H96" s="4" t="s">
-        <v>196</v>
+      <c r="H96" s="4">
+        <v>32</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
@@ -3945,11 +3762,11 @@
       <c r="G97" s="6">
         <v>0.7</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>197</v>
+      <c r="H97" s="3">
+        <v>35</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
@@ -3974,11 +3791,11 @@
       <c r="G98" s="6">
         <v>1</v>
       </c>
-      <c r="H98" s="4" t="s">
-        <v>198</v>
+      <c r="H98" s="4">
+        <v>37</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
@@ -4003,11 +3820,11 @@
       <c r="G99" s="6">
         <v>1</v>
       </c>
-      <c r="H99" s="4" t="s">
-        <v>200</v>
+      <c r="H99" s="4">
+        <v>27</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
@@ -4032,11 +3849,11 @@
       <c r="G100" s="6">
         <v>1</v>
       </c>
-      <c r="H100" s="4" t="s">
-        <v>201</v>
+      <c r="H100" s="4">
+        <v>30</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
@@ -4061,11 +3878,11 @@
       <c r="G101" s="6">
         <v>1</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>202</v>
+      <c r="H101" s="3">
+        <v>65</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
@@ -4073,7 +3890,7 @@
         <v>94</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="C102" s="3">
         <v>31007</v>
@@ -4090,11 +3907,11 @@
       <c r="G102" s="6">
         <v>1</v>
       </c>
-      <c r="H102" s="4" t="s">
-        <v>231</v>
+      <c r="H102" s="4">
+        <v>40</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
@@ -4102,7 +3919,7 @@
         <v>94</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="C103" s="3">
         <v>25583</v>
@@ -4119,11 +3936,11 @@
       <c r="G103" s="6">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H103" s="4" t="s">
-        <v>232</v>
+      <c r="H103" s="4">
+        <v>55</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
